--- a/1316_Cuenca_Locumba/_raw_reportes_xlsx/IDConfig_64964_completo.xlsx
+++ b/1316_Cuenca_Locumba/_raw_reportes_xlsx/IDConfig_64964_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R53213d2d9a4d4460"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd235b437820f434e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0106</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0146</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0138</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0174</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0171</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0213</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0159</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/1316_Cuenca_Locumba/_raw_reportes_xlsx/IDConfig_64964_completo.xlsx
+++ b/1316_Cuenca_Locumba/_raw_reportes_xlsx/IDConfig_64964_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd235b437820f434e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4dbab0b22efe4b90"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0123</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0114</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0098</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0011</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0148</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0127</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0066</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0068</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0061</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0084</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0089</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0097</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0086</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0106</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0093</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0107</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0129</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0091</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0148</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0087</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0095</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0127</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0097</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0157</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0116</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0099</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0067</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0087</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0122</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0123</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0211</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0176</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0121</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0142</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0106</x:v>
+        <x:v>      3.0129</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0155</x:v>
+        <x:v>      3.0165</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0197</x:v>
+        <x:v>      3.0188</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0197</x:v>
+        <x:v>      3.0221</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0149</x:v>
+        <x:v>      3.0178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0315</x:v>
+        <x:v>      3.0398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0442</x:v>
+        <x:v>      3.0475</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0534</x:v>
+        <x:v>      3.0535</x:v>
       </x:c>
     </x:row>
     <x:row>
